--- a/survey_templates/049_crime_novel_writing_survey--survey_templates.xlsx
+++ b/survey_templates/049_crime_novel_writing_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'experienced'}</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Experienced'}</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'plot'}</t>
+          <t>plot</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Plot'}</t>
+          <t>Plot</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'character'}</t>
+          <t>character</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Character'}</t>
+          <t>Character</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'pacing'}</t>
+          <t>pacing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Pacing'}</t>
+          <t>Pacing</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'theme'}</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Theme'}</t>
+          <t>Theme</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'crime'}</t>
+          <t>crime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Crime'}</t>
+          <t>Crime</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'science_fiction'}</t>
+          <t>science_fiction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Science Fiction'}</t>
+          <t>Science Fiction</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fantasy'}</t>
+          <t>fantasy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fantasy'}</t>
+          <t>Fantasy</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'strong_conflict'}</t>
+          <t>strong_conflict</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Strong Conflict'}</t>
+          <t>Strong Conflict</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'well-developed_characters'}</t>
+          <t>well-developed_characters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Well-Developed Characters'}</t>
+          <t>Well-Developed Characters</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'pacing'}</t>
+          <t>pacing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Pacing'}</t>
+          <t>Pacing</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'unique_voice'}</t>
+          <t>unique_voice</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Unique Voice'}</t>
+          <t>Unique Voice</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'commercial_appeal'}</t>
+          <t>commercial_appeal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial Appeal'}</t>
+          <t>Commercial Appeal</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'originality'}</t>
+          <t>originality</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Originality'}</t>
+          <t>Originality</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'marketability'}</t>
+          <t>marketability</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Marketability'}</t>
+          <t>Marketability</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'thematic_depth'}</t>
+          <t>thematic_depth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Thematic Depth'}</t>
+          <t>Thematic Depth</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'local_writing_group'}</t>
+          <t>local_writing_group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Local Writing Group'}</t>
+          <t>Local Writing Group</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'online_writing_group'}</t>
+          <t>online_writing_group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Online Writing Group'}</t>
+          <t>Online Writing Group</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'writing_conference'}</t>
+          <t>writing_conference</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Conference'}</t>
+          <t>Writing Conference</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'online_course'}</t>
+          <t>online_course</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Online Course'}</t>
+          <t>Online Course</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'writing_workshop'}</t>
+          <t>writing_workshop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Workshop'}</t>
+          <t>Writing Workshop</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'writing_conference'}</t>
+          <t>writing_conference</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Conference'}</t>
+          <t>Writing Conference</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'to_become_a_published_author'}</t>
+          <t>to_become_a_published_author</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'To Become a Published Author'}</t>
+          <t>To Become a Published Author</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'to_join_a_writing_group'}</t>
+          <t>to_join_a_writing_group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'To Join a Writing Group'}</t>
+          <t>To Join a Writing Group</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'to_learn_about_writing'}</t>
+          <t>to_learn_about_writing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'To Learn About Writing'}</t>
+          <t>To Learn About Writing</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'writing_books'}</t>
+          <t>writing_books</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Books'}</t>
+          <t>Writing Books</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'writing_conferences'}</t>
+          <t>writing_conferences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Conferences'}</t>
+          <t>Writing Conferences</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'writing_workshops'}</t>
+          <t>writing_workshops</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Writing Workshops'}</t>
+          <t>Writing Workshops</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'online_communities'}</t>
+          <t>online_communities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Online Communities'}</t>
+          <t>Online Communities</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
